--- a/Luban/Datas/BossPhase.xlsx
+++ b/Luban/Datas/BossPhase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lipenghui/LeanProject/LeiTing/Luban/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1224B339-6BDE-494E-8405-005C31FDD9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD919EA-6138-6846-9300-96B993FEF096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4420" yWindow="3660" windowWidth="26900" windowHeight="15860" xr2:uid="{FBB85636-24E0-7441-A6E2-7EACCDA44755}"/>
   </bookViews>
@@ -95,22 +95,13 @@
     <t>boss_helicopter_01_phase_01</t>
   </si>
   <si>
-    <t>PHASE 3  雷核过载</t>
-  </si>
-  <si>
     <t>boss_01</t>
   </si>
   <si>
     <t>boss_phase_03</t>
   </si>
   <si>
-    <t>PHASE 2  压迫提升</t>
-  </si>
-  <si>
     <t>boss_phase_02</t>
-  </si>
-  <si>
-    <t>PHASE 1  弹幕教学</t>
   </si>
   <si>
     <t>boss_phase_01</t>
@@ -199,6 +190,18 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>热身</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>恐惧</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -206,7 +209,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -251,6 +254,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111827"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -307,7 +317,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -323,6 +333,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -679,129 +692,129 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" ht="17">
       <c r="A4" s="2"/>
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -825,19 +838,19 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" ht="17">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="F5" s="2">
         <v>0.66</v>
@@ -861,19 +874,19 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" ht="17">
       <c r="A6" s="2"/>
       <c r="B6" s="2">
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="F6" s="2">
         <v>0.33</v>

--- a/Luban/Datas/BossPhase.xlsx
+++ b/Luban/Datas/BossPhase.xlsx
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -1121,48 +1121,6 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>boss_level1_enemy_08_phase_01</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>boss_level1_enemy_08</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>关卡1小型BOSS</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0.95</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
